--- a/ProyectoSoftwareSistemas/bin/Debug/output/sec2_ArchivoIntermedio.xlsx
+++ b/ProyectoSoftwareSistemas/bin/Debug/output/sec2_ArchivoIntermedio.xlsx
@@ -7,11 +7,12 @@
   </x:bookViews>
   <x:sheets>
     <x:sheet name="ArchivoIntermedio" sheetId="1" r:id="rId2"/>
-    <x:sheet name="ProgramaObjeto" sheetId="2" r:id="rId3"/>
-    <x:sheet name="TABSIM_DEFAULT" sheetId="3" r:id="rId4"/>
-    <x:sheet name="TABBLK_DEFAULT" sheetId="4" r:id="rId5"/>
-    <x:sheet name="TABSIM_PROG1" sheetId="5" r:id="rId6"/>
-    <x:sheet name="TABBLK_PROG1" sheetId="6" r:id="rId7"/>
+    <x:sheet name="ProgObj_PROG" sheetId="2" r:id="rId3"/>
+    <x:sheet name="ProgObj_PROG1" sheetId="3" r:id="rId4"/>
+    <x:sheet name="TABSIM_DEFAULT" sheetId="4" r:id="rId5"/>
+    <x:sheet name="TABBLK_DEFAULT" sheetId="5" r:id="rId6"/>
+    <x:sheet name="TABSIM_PROG1" sheetId="6" r:id="rId7"/>
+    <x:sheet name="TABBLK_PROG1" sheetId="7" r:id="rId8"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -210,10 +211,7 @@
     <x:t>LDB</x:t>
   </x:si>
   <x:si>
-    <x:t>Error: Símbolos externos requieren Formato 4 (+)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>693FFF</x:t>
+    <x:t>692003</x:t>
   </x:si>
   <x:si>
     <x:t>0006</x:t>
@@ -231,7 +229,7 @@
     <x:t>COUNT-TABLE+NUM1</x:t>
   </x:si>
   <x:si>
-    <x:t>FFFFFD*SE</x:t>
+    <x:t>000003*R*SE*SE</x:t>
   </x:si>
   <x:si>
     <x:t>1018</x:t>
@@ -240,21 +238,60 @@
     <x:t>END</x:t>
   </x:si>
   <x:si>
+    <x:t>Símbolo no definido: FIRST</x:t>
+  </x:si>
+  <x:si>
     <x:t>HPROG  000000001018</x:t>
   </x:si>
   <x:si>
-    <x:t>T0000001605000069100000*SE2F100000*SE0F900000*SE1BA003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T00000003693FFF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T00100604FFFFFD*SE</x:t>
+    <x:t xml:space="preserve">RNUM1  TABLE2PROG1 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCOUNT 000012TABLE 000015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00000012050000691000002F1000000F9000001BA003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M00000405+TABLE2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M00000805+NUM1  </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M00000C05+PROG1 </x:t>
   </x:si>
   <x:si>
     <x:t>E000000</x:t>
   </x:si>
   <x:si>
+    <x:t>HPROG1 000000001009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNUM1  000003TABLE2000006</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">RCOUNT TABLE </x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00000003692003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00100603000003</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M00100606+COUNT </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M00100606-TABLE </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M00100606+PROG1 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>E</x:t>
+  </x:si>
+  <x:si>
     <x:t>Simbolo</x:t>
   </x:si>
   <x:si>
@@ -268,9 +305,6 @@
   </x:si>
   <x:si>
     <x:t>SimboloExterno</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E</x:t>
   </x:si>
   <x:si>
     <x:t>Sí</x:t>
@@ -659,8 +693,8 @@
     <x:col min="6" max="6" width="20.567768" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="9.710625" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="44.853482" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="12.567768" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24.996339" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="15.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:10">
@@ -1201,10 +1235,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="J17" s="0" t="s">
-        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
@@ -1247,10 +1281,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>66</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
         <x:v>54</x:v>
@@ -1279,16 +1313,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="F20" s="0" t="s">
-        <x:v>69</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
         <x:v>14</x:v>
@@ -1300,7 +1334,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
@@ -1311,13 +1345,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
         <x:v>22</x:v>
@@ -1329,7 +1363,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
         <x:v>17</x:v>
@@ -1349,10 +1383,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:A5"/>
+  <x:dimension ref="A1:A8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="58.424911" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="48.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1">
@@ -1378,6 +1412,21 @@
     <x:row r="5" spans="1:1">
       <x:c r="A5" s="0" t="s">
         <x:v>77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:1">
+      <x:c r="A6" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:1">
+      <x:c r="A7" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:1">
+      <x:c r="A8" s="0" t="s">
+        <x:v>80</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1390,6 +1439,71 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:A9"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28.139196" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:1">
+      <x:c r="A1" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:1">
+      <x:c r="A2" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:1">
+      <x:c r="A3" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:1">
+      <x:c r="A4" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:1">
+      <x:c r="A5" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:1">
+      <x:c r="A6" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:1">
+      <x:c r="A7" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:1">
+      <x:c r="A8" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:1">
+      <x:c r="A9" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1406,19 +1520,19 @@
   <x:sheetData>
     <x:row r="1" spans="1:5">
       <x:c r="A1" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
@@ -1429,30 +1543,30 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
@@ -1463,13 +1577,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
@@ -1480,13 +1594,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
@@ -1497,13 +1611,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
@@ -1514,13 +1628,13 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
@@ -1531,13 +1645,13 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1549,7 +1663,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1564,16 +1678,16 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
@@ -1581,10 +1695,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
@@ -1599,7 +1713,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1616,19 +1730,19 @@
   <x:sheetData>
     <x:row r="1" spans="1:5">
       <x:c r="A1" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
@@ -1639,13 +1753,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -1656,13 +1770,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
@@ -1673,30 +1787,30 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
@@ -1704,16 +1818,16 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1725,7 +1839,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1740,16 +1854,16 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
@@ -1757,10 +1871,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
